--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="30240" windowHeight="12680"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -7438,7 +7438,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7474,9 +7474,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -14922,246 +14919,246 @@
       </c>
     </row>
     <row r="818" ht="17" customHeight="1" spans="1:4">
-      <c r="A818" s="12" t="s">
+      <c r="A818" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="B818" s="12" t="s">
+      <c r="B818" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="C818" s="12" t="s">
+      <c r="C818" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="D818" s="12" t="s">
+      <c r="D818" s="3" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="819" ht="17" customHeight="1" spans="1:4">
-      <c r="A819" s="12"/>
-      <c r="B819" s="12"/>
-      <c r="C819" s="12"/>
-      <c r="D819" s="12" t="s">
+      <c r="A819" s="3"/>
+      <c r="B819" s="3"/>
+      <c r="C819" s="3"/>
+      <c r="D819" s="3" t="s">
         <v>882</v>
       </c>
     </row>
     <row r="820" ht="17" customHeight="1" spans="1:4">
-      <c r="A820" s="12"/>
-      <c r="B820" s="12"/>
-      <c r="C820" s="12"/>
-      <c r="D820" s="12" t="s">
+      <c r="A820" s="3"/>
+      <c r="B820" s="3"/>
+      <c r="C820" s="3"/>
+      <c r="D820" s="3" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="821" ht="17" customHeight="1" spans="1:4">
-      <c r="A821" s="12"/>
-      <c r="B821" s="12"/>
-      <c r="C821" s="12"/>
-      <c r="D821" s="12" t="s">
+      <c r="A821" s="3"/>
+      <c r="B821" s="3"/>
+      <c r="C821" s="3"/>
+      <c r="D821" s="3" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="822" ht="17" customHeight="1" spans="1:4">
-      <c r="A822" s="12"/>
-      <c r="B822" s="12"/>
-      <c r="C822" s="12"/>
-      <c r="D822" s="12" t="s">
+      <c r="A822" s="3"/>
+      <c r="B822" s="3"/>
+      <c r="C822" s="3"/>
+      <c r="D822" s="3" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="823" ht="17" customHeight="1" spans="1:4">
-      <c r="A823" s="12"/>
-      <c r="B823" s="12"/>
-      <c r="C823" s="12"/>
-      <c r="D823" s="12" t="s">
+      <c r="A823" s="3"/>
+      <c r="B823" s="3"/>
+      <c r="C823" s="3"/>
+      <c r="D823" s="3" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="824" ht="17" customHeight="1" spans="1:4">
-      <c r="A824" s="12"/>
-      <c r="B824" s="12"/>
-      <c r="C824" s="12"/>
-      <c r="D824" s="12" t="s">
+      <c r="A824" s="3"/>
+      <c r="B824" s="3"/>
+      <c r="C824" s="3"/>
+      <c r="D824" s="3" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="825" ht="17" customHeight="1" spans="1:4">
-      <c r="A825" s="12"/>
-      <c r="B825" s="12"/>
-      <c r="C825" s="12"/>
-      <c r="D825" s="12" t="s">
+      <c r="A825" s="3"/>
+      <c r="B825" s="3"/>
+      <c r="C825" s="3"/>
+      <c r="D825" s="3" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="826" ht="17" customHeight="1" spans="1:4">
-      <c r="A826" s="12"/>
-      <c r="B826" s="12"/>
-      <c r="C826" s="12"/>
-      <c r="D826" s="12" t="s">
+      <c r="A826" s="3"/>
+      <c r="B826" s="3"/>
+      <c r="C826" s="3"/>
+      <c r="D826" s="3" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="827" ht="17" customHeight="1" spans="1:4">
-      <c r="A827" s="12"/>
-      <c r="B827" s="12"/>
-      <c r="C827" s="12"/>
-      <c r="D827" s="12" t="s">
+      <c r="A827" s="3"/>
+      <c r="B827" s="3"/>
+      <c r="C827" s="3"/>
+      <c r="D827" s="3" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="828" ht="17" customHeight="1" spans="1:4">
-      <c r="A828" s="12"/>
-      <c r="B828" s="12"/>
-      <c r="C828" s="12"/>
-      <c r="D828" s="12" t="s">
+      <c r="A828" s="3"/>
+      <c r="B828" s="3"/>
+      <c r="C828" s="3"/>
+      <c r="D828" s="3" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="829" ht="17" customHeight="1" spans="1:4">
-      <c r="A829" s="12"/>
-      <c r="B829" s="12"/>
-      <c r="C829" s="12"/>
-      <c r="D829" s="12" t="s">
+      <c r="A829" s="3"/>
+      <c r="B829" s="3"/>
+      <c r="C829" s="3"/>
+      <c r="D829" s="3" t="s">
         <v>892</v>
       </c>
     </row>
     <row r="830" ht="17" customHeight="1" spans="1:4">
-      <c r="A830" s="12"/>
-      <c r="B830" s="12"/>
-      <c r="C830" s="12"/>
-      <c r="D830" s="12" t="s">
+      <c r="A830" s="3"/>
+      <c r="B830" s="3"/>
+      <c r="C830" s="3"/>
+      <c r="D830" s="3" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="831" ht="17" customHeight="1" spans="1:4">
-      <c r="A831" s="12"/>
-      <c r="B831" s="12"/>
-      <c r="C831" s="12"/>
-      <c r="D831" s="12" t="s">
+      <c r="A831" s="3"/>
+      <c r="B831" s="3"/>
+      <c r="C831" s="3"/>
+      <c r="D831" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="832" ht="17" customHeight="1" spans="1:4">
-      <c r="A832" s="12" t="s">
+      <c r="A832" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="B832" s="12" t="s">
+      <c r="B832" s="3" t="s">
         <v>894</v>
       </c>
-      <c r="C832" s="12" t="s">
+      <c r="C832" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="D832" s="12" t="s">
+      <c r="D832" s="3" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="833" ht="17" customHeight="1" spans="1:4">
-      <c r="A833" s="12"/>
-      <c r="B833" s="12"/>
-      <c r="C833" s="12"/>
-      <c r="D833" s="12" t="s">
+      <c r="A833" s="3"/>
+      <c r="B833" s="3"/>
+      <c r="C833" s="3"/>
+      <c r="D833" s="3" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="834" ht="17" customHeight="1" spans="1:4">
-      <c r="A834" s="12"/>
-      <c r="B834" s="12"/>
-      <c r="C834" s="12"/>
-      <c r="D834" s="12" t="s">
+      <c r="A834" s="3"/>
+      <c r="B834" s="3"/>
+      <c r="C834" s="3"/>
+      <c r="D834" s="3" t="s">
         <v>897</v>
       </c>
     </row>
     <row r="835" ht="17" customHeight="1" spans="1:4">
-      <c r="A835" s="12"/>
-      <c r="B835" s="12"/>
-      <c r="C835" s="12"/>
-      <c r="D835" s="12" t="s">
+      <c r="A835" s="3"/>
+      <c r="B835" s="3"/>
+      <c r="C835" s="3"/>
+      <c r="D835" s="3" t="s">
         <v>898</v>
       </c>
     </row>
     <row r="836" ht="17" customHeight="1" spans="1:4">
-      <c r="A836" s="12"/>
-      <c r="B836" s="12"/>
-      <c r="C836" s="12"/>
-      <c r="D836" s="12" t="s">
+      <c r="A836" s="3"/>
+      <c r="B836" s="3"/>
+      <c r="C836" s="3"/>
+      <c r="D836" s="3" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="837" ht="17" customHeight="1" spans="1:4">
-      <c r="A837" s="12"/>
-      <c r="B837" s="12"/>
-      <c r="C837" s="12"/>
-      <c r="D837" s="12" t="s">
+      <c r="A837" s="3"/>
+      <c r="B837" s="3"/>
+      <c r="C837" s="3"/>
+      <c r="D837" s="3" t="s">
         <v>900</v>
       </c>
     </row>
     <row r="838" ht="17" customHeight="1" spans="1:4">
-      <c r="A838" s="12"/>
-      <c r="B838" s="12"/>
-      <c r="C838" s="12"/>
-      <c r="D838" s="12" t="s">
+      <c r="A838" s="3"/>
+      <c r="B838" s="3"/>
+      <c r="C838" s="3"/>
+      <c r="D838" s="3" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="839" ht="17" customHeight="1" spans="1:4">
-      <c r="A839" s="12"/>
-      <c r="B839" s="12"/>
-      <c r="C839" s="12"/>
-      <c r="D839" s="12" t="s">
+      <c r="A839" s="3"/>
+      <c r="B839" s="3"/>
+      <c r="C839" s="3"/>
+      <c r="D839" s="3" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="840" ht="17" customHeight="1" spans="1:4">
-      <c r="A840" s="12"/>
-      <c r="B840" s="12"/>
-      <c r="C840" s="12"/>
-      <c r="D840" s="12" t="s">
+      <c r="A840" s="3"/>
+      <c r="B840" s="3"/>
+      <c r="C840" s="3"/>
+      <c r="D840" s="3" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="841" ht="17" customHeight="1" spans="1:4">
-      <c r="A841" s="12"/>
-      <c r="B841" s="12"/>
-      <c r="C841" s="12"/>
-      <c r="D841" s="12" t="s">
+      <c r="A841" s="3"/>
+      <c r="B841" s="3"/>
+      <c r="C841" s="3"/>
+      <c r="D841" s="3" t="s">
         <v>903</v>
       </c>
     </row>
     <row r="842" ht="17" customHeight="1" spans="1:4">
-      <c r="A842" s="12"/>
-      <c r="B842" s="12"/>
-      <c r="C842" s="12"/>
-      <c r="D842" s="12" t="s">
+      <c r="A842" s="3"/>
+      <c r="B842" s="3"/>
+      <c r="C842" s="3"/>
+      <c r="D842" s="3" t="s">
         <v>904</v>
       </c>
     </row>
     <row r="843" ht="17" customHeight="1" spans="1:4">
-      <c r="A843" s="12"/>
-      <c r="B843" s="12"/>
-      <c r="C843" s="12"/>
-      <c r="D843" s="12" t="s">
+      <c r="A843" s="3"/>
+      <c r="B843" s="3"/>
+      <c r="C843" s="3"/>
+      <c r="D843" s="3" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="844" ht="17" customHeight="1" spans="1:4">
-      <c r="A844" s="12"/>
-      <c r="B844" s="12"/>
-      <c r="C844" s="12"/>
-      <c r="D844" s="12" t="s">
+      <c r="A844" s="3"/>
+      <c r="B844" s="3"/>
+      <c r="C844" s="3"/>
+      <c r="D844" s="3" t="s">
         <v>906</v>
       </c>
     </row>
     <row r="845" ht="17" customHeight="1" spans="1:4">
-      <c r="A845" s="12"/>
-      <c r="B845" s="12"/>
-      <c r="C845" s="12"/>
-      <c r="D845" s="12" t="s">
+      <c r="A845" s="3"/>
+      <c r="B845" s="3"/>
+      <c r="C845" s="3"/>
+      <c r="D845" s="3" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="846" ht="17" customHeight="1" spans="1:4">
-      <c r="A846" s="12"/>
-      <c r="B846" s="12"/>
-      <c r="C846" s="12"/>
-      <c r="D846" s="12" t="s">
+      <c r="A846" s="3"/>
+      <c r="B846" s="3"/>
+      <c r="C846" s="3"/>
+      <c r="D846" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -16198,13 +16195,13 @@
       </c>
     </row>
     <row r="970" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A970" s="13" t="s">
+      <c r="A970" s="12" t="s">
         <v>1033</v>
       </c>
-      <c r="B970" s="13" t="s">
+      <c r="B970" s="12" t="s">
         <v>1034</v>
       </c>
-      <c r="C970" s="13" t="s">
+      <c r="C970" s="12" t="s">
         <v>1035</v>
       </c>
       <c r="D970" s="10" t="s">
@@ -16212,73 +16209,73 @@
       </c>
     </row>
     <row r="971" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A971" s="14"/>
-      <c r="B971" s="14"/>
-      <c r="C971" s="14"/>
+      <c r="A971" s="13"/>
+      <c r="B971" s="13"/>
+      <c r="C971" s="13"/>
       <c r="D971" s="10" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="972" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A972" s="14"/>
-      <c r="B972" s="14"/>
-      <c r="C972" s="14"/>
+      <c r="A972" s="13"/>
+      <c r="B972" s="13"/>
+      <c r="C972" s="13"/>
       <c r="D972" s="10" t="s">
         <v>1038</v>
       </c>
     </row>
     <row r="973" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A973" s="14"/>
-      <c r="B973" s="14"/>
-      <c r="C973" s="14"/>
+      <c r="A973" s="13"/>
+      <c r="B973" s="13"/>
+      <c r="C973" s="13"/>
       <c r="D973" s="10" t="s">
         <v>1039</v>
       </c>
     </row>
     <row r="974" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A974" s="14"/>
-      <c r="B974" s="14"/>
-      <c r="C974" s="14"/>
+      <c r="A974" s="13"/>
+      <c r="B974" s="13"/>
+      <c r="C974" s="13"/>
       <c r="D974" s="10" t="s">
         <v>1040</v>
       </c>
     </row>
     <row r="975" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A975" s="14"/>
-      <c r="B975" s="14"/>
-      <c r="C975" s="14"/>
+      <c r="A975" s="13"/>
+      <c r="B975" s="13"/>
+      <c r="C975" s="13"/>
       <c r="D975" s="10" t="s">
         <v>1041</v>
       </c>
     </row>
     <row r="976" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A976" s="14"/>
-      <c r="B976" s="14"/>
-      <c r="C976" s="14"/>
+      <c r="A976" s="13"/>
+      <c r="B976" s="13"/>
+      <c r="C976" s="13"/>
       <c r="D976" s="10" t="s">
         <v>1042</v>
       </c>
     </row>
     <row r="977" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A977" s="14"/>
-      <c r="B977" s="14"/>
-      <c r="C977" s="14"/>
+      <c r="A977" s="13"/>
+      <c r="B977" s="13"/>
+      <c r="C977" s="13"/>
       <c r="D977" s="10" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="978" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A978" s="14"/>
-      <c r="B978" s="14"/>
-      <c r="C978" s="14"/>
+      <c r="A978" s="13"/>
+      <c r="B978" s="13"/>
+      <c r="C978" s="13"/>
       <c r="D978" s="10" t="s">
         <v>1044</v>
       </c>
     </row>
     <row r="979" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A979" s="15"/>
-      <c r="B979" s="15"/>
-      <c r="C979" s="15"/>
+      <c r="A979" s="14"/>
+      <c r="B979" s="14"/>
+      <c r="C979" s="14"/>
       <c r="D979" s="10" t="s">
         <v>71</v>
       </c>

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -1065,7 +1065,7 @@
     <t>4、点击2X，点击拍照</t>
   </si>
   <si>
-    <t>5、点击10X，点击拍照</t>
+    <t>5、点击10X，点击拍照（如果现在iPhone没有，调到最高倍）</t>
   </si>
   <si>
     <t>6、底部点击箭头拉起设置页面</t>
@@ -1098,7 +1098,7 @@
     <t>15、侧滑返回预览框</t>
   </si>
   <si>
-    <t>16、点击小艺视觉</t>
+    <t>16、点击小艺视觉（如果没有跳过）</t>
   </si>
   <si>
     <t>17、点击拍照</t>
@@ -1107,7 +1107,7 @@
     <t>18、侧滑返回扫一扫页面</t>
   </si>
   <si>
-    <t>19、点击小艺视觉页左侧图库图标拉起图库</t>
+    <t>19、点击左侧图库图标拉起图库（如果没有跳过）</t>
   </si>
   <si>
     <t>20、图库上滑3次，下滑3次</t>
@@ -1125,7 +1125,7 @@
     <t>相机切换模式</t>
   </si>
   <si>
-    <t>2、点击设置4X对焦</t>
+    <t>2、点击设置4X对焦（如果现在iPhone没有，调到最高倍）</t>
   </si>
   <si>
     <t>3、点击屏幕中间，拍摄一张照片，拍照5次</t>
@@ -1149,7 +1149,7 @@
     <t>9、点击录像切换到录像模式</t>
   </si>
   <si>
-    <t>10、录像设置为4X变焦、1080p60fps录像模式</t>
+    <t>10、录像设置为4X变焦（如果现在iPhone没有，调到最高倍）、1080p60fps录像模式</t>
   </si>
   <si>
     <t>11、开始录像</t>
@@ -6799,8 +6799,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -7308,16 +7315,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7326,46 +7330,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7374,10 +7381,10 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7386,10 +7393,10 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7398,10 +7405,10 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7410,10 +7417,10 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7422,10 +7429,10 @@
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7434,11 +7441,11 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7470,6 +7477,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -11014,7 +11024,7 @@
       <c r="A358" s="8"/>
       <c r="B358" s="8"/>
       <c r="C358" s="8"/>
-      <c r="D358" s="8" t="s">
+      <c r="D358" s="11" t="s">
         <v>383</v>
       </c>
     </row>
@@ -11022,7 +11032,7 @@
       <c r="A359" s="8"/>
       <c r="B359" s="8"/>
       <c r="C359" s="8"/>
-      <c r="D359" s="8" t="s">
+      <c r="D359" s="11" t="s">
         <v>384</v>
       </c>
     </row>
@@ -11030,7 +11040,7 @@
       <c r="A360" s="8"/>
       <c r="B360" s="8"/>
       <c r="C360" s="8"/>
-      <c r="D360" s="8" t="s">
+      <c r="D360" s="11" t="s">
         <v>385</v>
       </c>
     </row>
@@ -14560,7 +14570,7 @@
       <c r="A775" s="10"/>
       <c r="B775" s="10"/>
       <c r="C775" s="10"/>
-      <c r="D775" s="11" t="s">
+      <c r="D775" s="12" t="s">
         <v>832</v>
       </c>
     </row>
@@ -16195,13 +16205,13 @@
       </c>
     </row>
     <row r="970" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A970" s="12" t="s">
+      <c r="A970" s="13" t="s">
         <v>1033</v>
       </c>
-      <c r="B970" s="12" t="s">
+      <c r="B970" s="13" t="s">
         <v>1034</v>
       </c>
-      <c r="C970" s="12" t="s">
+      <c r="C970" s="13" t="s">
         <v>1035</v>
       </c>
       <c r="D970" s="10" t="s">
@@ -16209,73 +16219,73 @@
       </c>
     </row>
     <row r="971" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A971" s="13"/>
-      <c r="B971" s="13"/>
-      <c r="C971" s="13"/>
+      <c r="A971" s="14"/>
+      <c r="B971" s="14"/>
+      <c r="C971" s="14"/>
       <c r="D971" s="10" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="972" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A972" s="13"/>
-      <c r="B972" s="13"/>
-      <c r="C972" s="13"/>
+      <c r="A972" s="14"/>
+      <c r="B972" s="14"/>
+      <c r="C972" s="14"/>
       <c r="D972" s="10" t="s">
         <v>1038</v>
       </c>
     </row>
     <row r="973" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A973" s="13"/>
-      <c r="B973" s="13"/>
-      <c r="C973" s="13"/>
+      <c r="A973" s="14"/>
+      <c r="B973" s="14"/>
+      <c r="C973" s="14"/>
       <c r="D973" s="10" t="s">
         <v>1039</v>
       </c>
     </row>
     <row r="974" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A974" s="13"/>
-      <c r="B974" s="13"/>
-      <c r="C974" s="13"/>
+      <c r="A974" s="14"/>
+      <c r="B974" s="14"/>
+      <c r="C974" s="14"/>
       <c r="D974" s="10" t="s">
         <v>1040</v>
       </c>
     </row>
     <row r="975" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A975" s="13"/>
-      <c r="B975" s="13"/>
-      <c r="C975" s="13"/>
+      <c r="A975" s="14"/>
+      <c r="B975" s="14"/>
+      <c r="C975" s="14"/>
       <c r="D975" s="10" t="s">
         <v>1041</v>
       </c>
     </row>
     <row r="976" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A976" s="13"/>
-      <c r="B976" s="13"/>
-      <c r="C976" s="13"/>
+      <c r="A976" s="14"/>
+      <c r="B976" s="14"/>
+      <c r="C976" s="14"/>
       <c r="D976" s="10" t="s">
         <v>1042</v>
       </c>
     </row>
     <row r="977" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A977" s="13"/>
-      <c r="B977" s="13"/>
-      <c r="C977" s="13"/>
+      <c r="A977" s="14"/>
+      <c r="B977" s="14"/>
+      <c r="C977" s="14"/>
       <c r="D977" s="10" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="978" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A978" s="13"/>
-      <c r="B978" s="13"/>
-      <c r="C978" s="13"/>
+      <c r="A978" s="14"/>
+      <c r="B978" s="14"/>
+      <c r="C978" s="14"/>
       <c r="D978" s="10" t="s">
         <v>1044</v>
       </c>
     </row>
     <row r="979" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A979" s="14"/>
-      <c r="B979" s="14"/>
-      <c r="C979" s="14"/>
+      <c r="A979" s="15"/>
+      <c r="B979" s="15"/>
+      <c r="C979" s="15"/>
       <c r="D979" s="10" t="s">
         <v>71</v>
       </c>
